--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$194</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6294" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6327" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1886,6 +1886,21 @@
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR226.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>Type de diplôme, par exemple : DE, DES, CES, etc.</t>
+  </si>
+  <si>
+    <t>typeDiplome</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.text</t>
@@ -2243,7 +2258,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ193"/>
+  <dimension ref="A1:AJ194"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.60546875" customWidth="true" bestFit="true"/>
@@ -9880,7 +9895,7 @@
         <v>90</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" hidden="true">
@@ -21728,9 +21743,11 @@
         <v>605</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C190" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="D190" t="s" s="2">
         <v>71</v>
       </c>
@@ -21739,10 +21756,10 @@
         <v>72</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>71</v>
@@ -21751,19 +21768,19 @@
         <v>79</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>233</v>
+        <v>607</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>235</v>
+        <v>608</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>71</v>
@@ -21788,13 +21805,11 @@
         <v>71</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>71</v>
+        <v>609</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>71</v>
@@ -21812,13 +21827,13 @@
         <v>71</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>90</v>
@@ -21829,10 +21844,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21852,22 +21867,22 @@
         <v>71</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>252</v>
+        <v>166</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>607</v>
+        <v>233</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>608</v>
+        <v>234</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>609</v>
+        <v>236</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>71</v>
@@ -21916,7 +21931,7 @@
         <v>71</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>606</v>
+        <v>237</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>72</v>
@@ -21928,15 +21943,15 @@
         <v>90</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>257</v>
+        <v>91</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21959,18 +21974,20 @@
         <v>71</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O192" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>614</v>
+      </c>
       <c r="P192" t="s" s="2">
         <v>71</v>
       </c>
@@ -22018,7 +22035,7 @@
         <v>71</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>72</v>
@@ -22030,15 +22047,15 @@
         <v>90</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22049,10 +22066,10 @@
         <v>72</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H193" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I193" t="s" s="2">
         <v>71</v>
@@ -22061,7 +22078,7 @@
         <v>71</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>615</v>
+        <v>259</v>
       </c>
       <c r="L193" t="s" s="2">
         <v>616</v>
@@ -22072,9 +22089,7 @@
       <c r="N193" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="O193" t="s" s="2">
-        <v>619</v>
-      </c>
+      <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>71</v>
       </c>
@@ -22098,11 +22113,13 @@
         <v>71</v>
       </c>
       <c r="X193" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y193" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="Z193" t="s" s="2">
-        <v>620</v>
+        <v>71</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>71</v>
@@ -22120,23 +22137,125 @@
         <v>71</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ193" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="194" hidden="true">
+      <c r="A194" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G194" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H194" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="P194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q194" s="2"/>
+      <c r="R194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y194" s="2"/>
+      <c r="Z194" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
         <v>91</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ193">
+  <autoFilter ref="A1:AJ194">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -22146,7 +22265,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI192">
+  <conditionalFormatting sqref="A2:AI193">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
